--- a/Mediciones/RNA/Cruz/RUN1_CRUZ_2NO.xlsx
+++ b/Mediciones/RNA/Cruz/RUN1_CRUZ_2NO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GiHub\Resultados_Doc\Mediciones\RNA\Cruz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5D3FE4-584D-4003-A101-F56E0768E998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B02796A-8730-4FE2-868E-EEA9F7314E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -329,6 +329,9 @@
     <t>sensors_n_now</t>
   </si>
   <si>
+    <t>RNA</t>
+  </si>
+  <si>
     <t>{
   "timestamp": "2026-07-18T22:19:11",
   "bounds": {
@@ -339,7 +342,7 @@
   },
   "serial": {
     "port": "COM7",
-    "baud": "460800",
+    "baud": "115200",
     "eol": "LF",
     "send_enabled": true
   },
@@ -430,9 +433,6 @@
   "run_id": "R20260718_221911",
   "repetition": 1
 }</t>
-  </si>
-  <si>
-    <t>RNA</t>
   </si>
 </sst>
 </file>
@@ -788,7 +788,7 @@
     </row>
     <row r="2" spans="1:1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -889,7 +889,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D2">
         <v>1.6691565454990901E-2</v>
@@ -942,7 +942,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D3">
         <v>1.6691565454990901E-2</v>
@@ -995,7 +995,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>1.6691565454990901E-2</v>
@@ -1048,7 +1048,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>1.6691565454990901E-2</v>
@@ -1101,7 +1101,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>1.6691565454990901E-2</v>
@@ -1154,7 +1154,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>1.6691565454990901E-2</v>
@@ -1207,7 +1207,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>1.6691565454990901E-2</v>
@@ -1260,7 +1260,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>1.6691565454990901E-2</v>
@@ -1313,7 +1313,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>1.6691565454990901E-2</v>
@@ -1366,7 +1366,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>1.6691565454990901E-2</v>
@@ -1419,7 +1419,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>1.6691565454990901E-2</v>
@@ -1472,7 +1472,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>1.6691565454990901E-2</v>
@@ -1525,7 +1525,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>1.717392814886921E-2</v>
@@ -1578,7 +1578,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>1.717392814886921E-2</v>
@@ -1631,7 +1631,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>1.717392814886921E-2</v>
@@ -1684,7 +1684,7 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>1.717392814886921E-2</v>
@@ -1737,7 +1737,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>1.717392814886921E-2</v>
@@ -1790,7 +1790,7 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>1.717392814886921E-2</v>
@@ -1843,7 +1843,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>1.717392814886921E-2</v>
@@ -1896,7 +1896,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>1.717392814886921E-2</v>
@@ -1949,7 +1949,7 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>1.717392814886921E-2</v>
@@ -2002,7 +2002,7 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>1.717392814886921E-2</v>
@@ -2055,7 +2055,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>1.717392814886921E-2</v>
@@ -2108,7 +2108,7 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>1.717392814886921E-2</v>
@@ -2161,7 +2161,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>1.717392814886921E-2</v>
@@ -2214,7 +2214,7 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>2.1247107586365849E-2</v>
@@ -2267,7 +2267,7 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>2.1247107586365849E-2</v>
@@ -2320,7 +2320,7 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>2.1247107586365849E-2</v>
@@ -2373,7 +2373,7 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>2.1247107586365849E-2</v>
@@ -2426,7 +2426,7 @@
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>2.1247107586365849E-2</v>
@@ -2479,7 +2479,7 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D32">
         <v>2.1247107586365849E-2</v>
@@ -2532,7 +2532,7 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>2.1247107586365849E-2</v>
@@ -2585,7 +2585,7 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D34">
         <v>3.1845864605563393E-2</v>
@@ -2638,7 +2638,7 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>0.13642083337306449</v>
@@ -2691,7 +2691,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>0.53863460859331846</v>
@@ -2744,7 +2744,7 @@
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D37">
         <v>0.90653329030971719</v>
@@ -2797,7 +2797,7 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D38">
         <v>0.99321757593298721</v>
@@ -2850,7 +2850,7 @@
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D39">
         <v>0.99321757593298721</v>
@@ -2903,7 +2903,7 @@
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D40">
         <v>0.99321757593298721</v>
@@ -2956,7 +2956,7 @@
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D41">
         <v>0.99321757593298721</v>
@@ -3009,7 +3009,7 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D42">
         <v>0.99321757593298721</v>
@@ -3062,7 +3062,7 @@
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D43">
         <v>0.99321757593298721</v>
@@ -3115,7 +3115,7 @@
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D44">
         <v>0.99321757593298721</v>
@@ -3168,7 +3168,7 @@
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D45">
         <v>0.99321757593298721</v>
@@ -3221,7 +3221,7 @@
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D46">
         <v>0.99321757593298721</v>
@@ -3274,7 +3274,7 @@
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D47">
         <v>0.99321757593298721</v>
@@ -3327,7 +3327,7 @@
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D48">
         <v>0.99321757593298721</v>
@@ -3380,7 +3380,7 @@
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D49">
         <v>0.99321757593298721</v>
@@ -3433,7 +3433,7 @@
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D50">
         <v>0.99321757593298721</v>
@@ -3486,7 +3486,7 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D51">
         <v>0.99321757593298721</v>
@@ -3539,7 +3539,7 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D52">
         <v>0.99321757593298721</v>
@@ -3592,7 +3592,7 @@
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D53">
         <v>0.99321757593298721</v>
@@ -3645,7 +3645,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D54">
         <v>0.99321757593298721</v>
@@ -3698,7 +3698,7 @@
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D55">
         <v>0.99321757593298721</v>
@@ -3751,7 +3751,7 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D56">
         <v>0.99321757593298721</v>
@@ -3804,7 +3804,7 @@
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D57">
         <v>0.99321757593298721</v>
@@ -3857,7 +3857,7 @@
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D58">
         <v>0.99321757593298721</v>
@@ -3910,7 +3910,7 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D59">
         <v>0.99321757593298721</v>
@@ -3963,7 +3963,7 @@
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D60">
         <v>0.99321757593298721</v>
@@ -4016,7 +4016,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D61">
         <v>0.99321757593298721</v>
@@ -4069,7 +4069,7 @@
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D62">
         <v>0.99321757593298721</v>
@@ -4122,7 +4122,7 @@
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D63">
         <v>0.99321757593298721</v>
@@ -4175,7 +4175,7 @@
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D64">
         <v>0.99321757593298721</v>
@@ -4228,7 +4228,7 @@
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D65">
         <v>0.99321757593298721</v>
@@ -4281,7 +4281,7 @@
         <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D66">
         <v>0.99321757593298721</v>
@@ -4334,7 +4334,7 @@
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D67">
         <v>0.99321757593298721</v>
@@ -4387,7 +4387,7 @@
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D68">
         <v>0.99321757593298721</v>
@@ -4440,7 +4440,7 @@
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D69">
         <v>0.99321757593298721</v>
@@ -4493,7 +4493,7 @@
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D70">
         <v>0.99321757593298721</v>
@@ -4546,7 +4546,7 @@
         <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D71">
         <v>0.99321757593298721</v>
@@ -4599,7 +4599,7 @@
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D72">
         <v>0.99321757593298721</v>
@@ -4652,7 +4652,7 @@
         <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D73">
         <v>0.99321757593298721</v>
@@ -4705,7 +4705,7 @@
         <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D74">
         <v>0.99321757593298721</v>
@@ -4758,7 +4758,7 @@
         <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D75">
         <v>0.99321757593298721</v>
@@ -4811,7 +4811,7 @@
         <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D76">
         <v>0.99321757593298721</v>
@@ -4864,7 +4864,7 @@
         <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D77">
         <v>0.99321757593298721</v>
@@ -4917,7 +4917,7 @@
         <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D78">
         <v>0.99321757593298721</v>
@@ -4970,7 +4970,7 @@
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D79">
         <v>0.99321757593298721</v>
@@ -5023,7 +5023,7 @@
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D80">
         <v>0.99321757593298721</v>
@@ -5076,7 +5076,7 @@
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D81">
         <v>0.99321757593298721</v>
@@ -5129,7 +5129,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D82">
         <v>0.99321757593298721</v>
@@ -5182,7 +5182,7 @@
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D83">
         <v>0.99321757593298721</v>
@@ -5235,7 +5235,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D84">
         <v>0.99321757593298721</v>
@@ -5288,7 +5288,7 @@
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D85">
         <v>0.99321757593298721</v>
@@ -5341,7 +5341,7 @@
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D86">
         <v>0.99321757593298721</v>
@@ -5394,7 +5394,7 @@
         <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D87">
         <v>0.99321757593298721</v>
@@ -5447,7 +5447,7 @@
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D88">
         <v>0.99321757593298721</v>
@@ -5500,7 +5500,7 @@
         <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D89">
         <v>0.99321757593298721</v>
@@ -5553,7 +5553,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D90">
         <v>0.99321757593298721</v>
@@ -5606,7 +5606,7 @@
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D91">
         <v>0.99321757593298721</v>
@@ -5659,7 +5659,7 @@
         <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D92">
         <v>0.99321757593298721</v>
@@ -5712,7 +5712,7 @@
         <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D93">
         <v>0.99321757593298721</v>
@@ -5765,7 +5765,7 @@
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D94">
         <v>0.99321757593298721</v>
@@ -5818,7 +5818,7 @@
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D95">
         <v>0.99321757593298721</v>
@@ -5871,7 +5871,7 @@
         <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D96">
         <v>0.99321757593298721</v>
@@ -5924,7 +5924,7 @@
         <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D97">
         <v>0.99321757593298721</v>
@@ -5977,7 +5977,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D98">
         <v>0.99321757593298721</v>
@@ -6030,7 +6030,7 @@
         <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D99">
         <v>0.99321757593298721</v>
@@ -6083,7 +6083,7 @@
         <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D100">
         <v>0.99321757593298721</v>
@@ -6136,7 +6136,7 @@
         <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D101">
         <v>0.99321757593298721</v>
@@ -6189,7 +6189,7 @@
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D102">
         <v>0.99321757593298721</v>
@@ -6242,7 +6242,7 @@
         <v>101</v>
       </c>
       <c r="C103" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D103">
         <v>0.99321757593298721</v>
@@ -6295,7 +6295,7 @@
         <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D104">
         <v>0.99321757593298721</v>
@@ -6348,7 +6348,7 @@
         <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D105">
         <v>0.99321757593298721</v>
@@ -6401,7 +6401,7 @@
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D106">
         <v>0.99321757593298721</v>
@@ -6454,7 +6454,7 @@
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D107">
         <v>0.99321757593298721</v>
@@ -6507,7 +6507,7 @@
         <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D108">
         <v>0.99321757593298721</v>
@@ -6560,7 +6560,7 @@
         <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D109">
         <v>0.99321757593298721</v>
@@ -6613,7 +6613,7 @@
         <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D110">
         <v>0.99321757593298721</v>
@@ -6666,7 +6666,7 @@
         <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D111">
         <v>0.99321757593298721</v>
@@ -6719,7 +6719,7 @@
         <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D112">
         <v>0.99321757593298721</v>
@@ -6772,7 +6772,7 @@
         <v>111</v>
       </c>
       <c r="C113" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D113">
         <v>0.99321757593298721</v>
@@ -6825,7 +6825,7 @@
         <v>112</v>
       </c>
       <c r="C114" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D114">
         <v>0.99321757593298721</v>
@@ -6878,7 +6878,7 @@
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D115">
         <v>0.99321757593298721</v>
@@ -6931,7 +6931,7 @@
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D116">
         <v>0.99321757593298721</v>
@@ -6984,7 +6984,7 @@
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D117">
         <v>0.99321757593298721</v>
@@ -7037,7 +7037,7 @@
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D118">
         <v>0.99321757593298721</v>
@@ -7090,7 +7090,7 @@
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D119">
         <v>0.99321757593298721</v>
@@ -7143,7 +7143,7 @@
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D120">
         <v>0.99321757593298721</v>
@@ -7196,7 +7196,7 @@
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D121">
         <v>0.99321757593298721</v>
@@ -11059,7 +11059,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
